--- a/output/full_scan/batch_seq0_2026-07-20.xlsx
+++ b/output/full_scan/batch_seq0_2026-07-20.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O114"/>
+  <dimension ref="A1:O117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>8071</v>
+        <v>8383</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>732.4965279072387</v>
+        <v>795.3211580054405</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>24.4</v>
+        <v>80.2</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>41.05627107903689</v>
+        <v>61.3563592290823</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>34.26402550344353</v>
+        <v>36.90448010138506</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.2473650276605802</v>
+        <v>0.6321158005440428</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-1.106848319687478</v>
+        <v>2.079611518756677</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>8462</v>
+        <v>8071</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>636.221362469166</v>
+        <v>732.4965279072387</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>155.5</v>
+        <v>24.4</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>57.97526416209708</v>
+        <v>41.05627107903689</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>36.65661207311133</v>
+        <v>34.26402550344353</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.4937722772434145</v>
+        <v>0.2473650276605802</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.6943920881764907</v>
+        <v>-1.106848319687478</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8109</v>
+        <v>8462</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>633.752990841331</v>
+        <v>636.221362469166</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>128.5</v>
+        <v>155.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>46.61354002758876</v>
+        <v>57.97526416209708</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>26.76964689418284</v>
+        <v>36.65661207311133</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.5275940443124815</v>
+        <v>0.4937722772434145</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-1.605070152351994</v>
+        <v>0.6943920881764907</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>8289</v>
+        <v>8109</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>626.0525608368998</v>
+        <v>633.752990841331</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>44.7</v>
+        <v>128.5</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>26.35090496670028</v>
+        <v>46.61354002758876</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>22.77280686091278</v>
+        <v>26.76964689418284</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.5299110421579442</v>
+        <v>0.5275940443124815</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-1.738844914564071</v>
+        <v>-1.605070152351994</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>8091</v>
+        <v>8289</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>615.1417796543598</v>
+        <v>626.0525608368998</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>241.5</v>
+        <v>44.7</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>41.35182104505174</v>
+        <v>26.35090496670028</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>23.00899116870628</v>
+        <v>22.77280686091278</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.9652856960572744</v>
+        <v>0.5299110421579442</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-4.290182026413291</v>
+        <v>-1.738844914564071</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>8150</v>
+        <v>8091</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>603.115915053117</v>
+        <v>615.1417796543598</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>103</v>
+        <v>241.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>48.95385911234578</v>
+        <v>41.35182104505174</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>26.27694445253212</v>
+        <v>23.00899116870628</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.7050384218589778</v>
+        <v>0.9652856960572744</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.5620708871060192</v>
+        <v>-4.290182026413291</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -845,21 +845,21 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>8367</v>
+        <v>8150</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>564.0816538155207</v>
+        <v>603.115915053117</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>40.7</v>
+        <v>103</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>53.13596228117151</v>
+        <v>48.95385911234578</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>28.0273199870218</v>
+        <v>26.27694445253212</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.5968491422054172</v>
+        <v>0.7050384218589778</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.07929209307277491</v>
+        <v>-0.5620708871060192</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8155</v>
+        <v>8367</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>561.7362985721506</v>
+        <v>564.0816538155207</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>282</v>
+        <v>40.7</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>25.35922780479945</v>
+        <v>53.13596228117151</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>23.9711856091984</v>
+        <v>28.0273199870218</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.160513380394141</v>
+        <v>0.5968491422054172</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-7.950652498925368</v>
+        <v>0.07929209307277491</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8411</v>
+        <v>8155</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>544.7843101201854</v>
+        <v>561.7362985721506</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>12.6</v>
+        <v>282</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>61.05090394543221</v>
+        <v>25.35922780479945</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>20.7988837358909</v>
+        <v>23.9711856091984</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.5688712337875449</v>
+        <v>2.160513380394141</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.0332744926036658</v>
+        <v>-7.950652498925368</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8050</v>
+        <v>8411</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>543.8089052891864</v>
+        <v>544.7843101201854</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>55.6</v>
+        <v>12.6</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>47.41337549136543</v>
+        <v>61.05090394543221</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>25.50821236064068</v>
+        <v>20.7988837358909</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.9681053917473508</v>
+        <v>0.5688712337875449</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.0502230215828642</v>
+        <v>0.0332744926036658</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8438</v>
+        <v>8050</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>538.1280823870151</v>
+        <v>543.8089052891864</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>71.09999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>29.26113520221377</v>
+        <v>47.41337549136543</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>25.82997947844575</v>
+        <v>25.50821236064068</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2.456817914136796</v>
+        <v>0.9681053917473508</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-2.985334002173479</v>
+        <v>-0.0502230215828642</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8476</v>
+        <v>8438</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>535.2277799674955</v>
+        <v>538.1280823870151</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>24.35</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>64.4889547275572</v>
+        <v>29.26113520221377</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>39.24368613637008</v>
+        <v>25.82997947844575</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.6823670038997799</v>
+        <v>2.456817914136796</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.2181426586709516</v>
+        <v>-2.985334002173479</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8996</v>
+        <v>8476</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>529.4329150217334</v>
+        <v>535.2277799674955</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>971</v>
+        <v>24.35</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>31.61825428526758</v>
+        <v>64.4889547275572</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>23.19446785403177</v>
+        <v>39.24368613637008</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2.378840215057157</v>
+        <v>0.6823670038997799</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-56.12320165194066</v>
+        <v>-0.2181426586709516</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>9912</v>
+        <v>8996</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>521.4114569242587</v>
+        <v>529.4329150217334</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>12.6</v>
+        <v>971</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>50.22345738834519</v>
+        <v>31.61825428526758</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>18.16604411827472</v>
+        <v>23.19446785403177</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.2055904027789353</v>
+        <v>2.378840215057157</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.0022878288788672</v>
+        <v>-56.12320165194066</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8464</v>
+        <v>9912</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>519.9023864328175</v>
+        <v>521.4114569242587</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>360</v>
+        <v>12.6</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>53.7464431493932</v>
+        <v>50.22345738834519</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>24.78224988608148</v>
+        <v>18.16604411827472</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.9197641759172968</v>
+        <v>0.2055904027789353</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-1.345887768581846</v>
+        <v>-0.0022878288788672</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8182</v>
+        <v>8464</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>515.8127775889877</v>
+        <v>519.9023864328175</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>39.7</v>
+        <v>360</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>37.41032868653702</v>
+        <v>53.7464431493932</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>21.2500521241284</v>
+        <v>24.78224988608148</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.2034041549150358</v>
+        <v>0.9197641759172968</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-1.704560270827079</v>
+        <v>-1.345887768581846</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8271</v>
+        <v>8182</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>502.1141714103779</v>
+        <v>515.8127775889877</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>184</v>
+        <v>39.7</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>42.58524625652541</v>
+        <v>37.41032868653702</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>24.27960979013329</v>
+        <v>21.2500521241284</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.384325680930195</v>
+        <v>0.2034041549150358</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.7486613957583117</v>
+        <v>-1.704560270827079</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1428,21 +1428,21 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8482</v>
+        <v>8271</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>491.6032578339965</v>
+        <v>502.1141714103779</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>48.75</v>
+        <v>184</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>51.7543539425529</v>
+        <v>42.58524625652541</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>4.957580825594084</v>
+        <v>24.27960979013329</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>3.01531319165782</v>
+        <v>1.384325680930195</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.5559110662961007</v>
+        <v>0.7486613957583117</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8183</v>
+        <v>8482</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>491.5665803592696</v>
+        <v>491.6032578339965</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>30</v>
+        <v>48.75</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>36.56656772336066</v>
+        <v>51.7543539425529</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>23.5370900151153</v>
+        <v>4.957580825594084</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.4679446573358414</v>
+        <v>3.01531319165782</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.462545128125255</v>
+        <v>0.5559110662961007</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8358</v>
+        <v>8183</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>482.8252271388071</v>
+        <v>491.5665803592696</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>371</v>
+        <v>30</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>27.90431223654707</v>
+        <v>36.56656772336066</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>17.96011505973614</v>
+        <v>23.5370900151153</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.7189089305518133</v>
+        <v>0.4679446573358414</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-23.60176628451044</v>
+        <v>-0.462545128125255</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8074</v>
+        <v>8358</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>475.9522450423017</v>
+        <v>482.8252271388071</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>53.7</v>
+        <v>371</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,49 +1612,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>27.48885430352295</v>
+        <v>27.90431223654707</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>27.39091018765874</v>
+        <v>17.96011505973614</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.8414725066825216</v>
+        <v>0.7189089305518133</v>
       </c>
       <c r="K22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L22" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-1.135340347635904</v>
+        <v>-23.60176628451044</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8234</v>
+        <v>8074</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>473.2163611007624</v>
+        <v>475.9522450423017</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>58.7</v>
+        <v>53.7</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>35.80936045123424</v>
+        <v>27.48885430352295</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>22.31134913511922</v>
+        <v>27.39091018765874</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.4528140258123299</v>
+        <v>0.8414725066825216</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-1.126276195057965</v>
+        <v>-1.135340347635904</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8121</v>
+        <v>8234</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>472.8271411151015</v>
+        <v>473.2163611007624</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>33.8</v>
+        <v>58.7</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>31.01959071655206</v>
+        <v>35.80936045123424</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>25.79948406182832</v>
+        <v>22.31134913511922</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.6089438655896472</v>
+        <v>0.4528140258123299</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-1.769140250795477</v>
+        <v>-1.126276195057965</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8064</v>
+        <v>8121</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>470.6621589515572</v>
+        <v>472.8271411151015</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>108</v>
+        <v>33.8</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>34.62638224340604</v>
+        <v>31.01959071655206</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>16.95087664309198</v>
+        <v>25.79948406182832</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.7544964246122771</v>
+        <v>0.6089438655896472</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-3.592442841308582</v>
+        <v>-1.769140250795477</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8222</v>
+        <v>8291</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>463.1621837889962</v>
+        <v>470.7463275582508</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>37.8</v>
+        <v>33.05</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>46.91767791103925</v>
+        <v>40.82711779479388</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>27.24257552508554</v>
+        <v>31.88783227388325</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.9563125982760518</v>
+        <v>0.1396337922733177</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.3800918433855049</v>
+        <v>0.1446950747342228</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8227</v>
+        <v>8064</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>463.0937597040056</v>
+        <v>470.6621589515572</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>142.5</v>
+        <v>108</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>31.26528100458584</v>
+        <v>34.62638224340604</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>19.70404026439344</v>
+        <v>16.95087664309198</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.4401636614987188</v>
+        <v>0.7544964246122771</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-5.782000921745363</v>
+        <v>-3.592442841308582</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>9908</v>
+        <v>8222</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>大台北</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>462.0842696738495</v>
+        <v>463.1621837889962</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>29.1</v>
+        <v>37.8</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>36.22165888787202</v>
+        <v>46.91767791103925</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>24.33206912351723</v>
+        <v>27.24257552508554</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.799767829613555</v>
+        <v>0.9563125982760518</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.09436723757039529</v>
+        <v>-0.3800918433855049</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8086</v>
+        <v>8227</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>461.0828955572761</v>
+        <v>463.0937597040056</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>115</v>
+        <v>142.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>28.37874684555842</v>
+        <v>31.26528100458584</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>22.11089860590064</v>
+        <v>19.70404026439344</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.8669990470277117</v>
+        <v>0.4401636614987188</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-2.595418119352227</v>
+        <v>-5.782000921745363</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8163</v>
+        <v>9908</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>大台北</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>454.644685378633</v>
+        <v>462.0842696738495</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>32.5</v>
+        <v>29.1</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>32.99370978676362</v>
+        <v>36.22165888787202</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>25.44857883322119</v>
+        <v>24.33206912351723</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.5153588422073061</v>
+        <v>1.799767829613555</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-1.073116841435888</v>
+        <v>-0.09436723757039529</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>9105</v>
+        <v>8096</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>453.2626265858052</v>
+        <v>461.9968365404445</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>8.43</v>
+        <v>128</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>42.31981542603865</v>
+        <v>39.64939700254032</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>20.5947634684721</v>
+        <v>27.66239680319825</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.6949963680965144</v>
+        <v>0.2851862420929087</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.1381093433188907</v>
+        <v>-4.970931627071428</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8069</v>
+        <v>8086</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>452.552231795313</v>
+        <v>461.0828955572761</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>175.5</v>
+        <v>115</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,49 +2142,49 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>33.39594313084636</v>
+        <v>28.37874684555842</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>15.81293042210594</v>
+        <v>22.11089860590064</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.7430510961542823</v>
+        <v>0.8669990470277117</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-3.020169442121304</v>
+        <v>-2.595418119352227</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8374</v>
+        <v>8163</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>447.9414560005962</v>
+        <v>454.644685378633</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>75.8</v>
+        <v>32.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>32.91573495204673</v>
+        <v>32.99370978676362</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>13.25219277200956</v>
+        <v>25.44857883322119</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.6095493747103341</v>
+        <v>0.5153588422073061</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.9981366350124444</v>
+        <v>-1.073116841435888</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8081</v>
+        <v>9105</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>446.2790107926707</v>
+        <v>453.2626265858052</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>233.5</v>
+        <v>8.43</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>28.96192247879989</v>
+        <v>42.31981542603865</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>29.60056532615773</v>
+        <v>20.5947634684721</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.5443744957123356</v>
+        <v>0.6949963680965144</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-9.497274653187072</v>
+        <v>-0.1381093433188907</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2276,21 +2276,21 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8102</v>
+        <v>8069</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>445.0439504553092</v>
+        <v>452.552231795313</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>72.09999999999999</v>
+        <v>175.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,49 +2301,49 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>53.1024251651211</v>
+        <v>33.39594313084636</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>16.88612787101469</v>
+        <v>15.81293042210594</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.6139064712739905</v>
+        <v>0.7430510961542823</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.4824865957975249</v>
+        <v>-3.020169442121304</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8067</v>
+        <v>8374</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>443.309956566461</v>
+        <v>447.9414560005962</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>13.45</v>
+        <v>75.8</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>52.43430812175527</v>
+        <v>32.91573495204673</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>4.898404389446418</v>
+        <v>13.25219277200956</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.1045182362547632</v>
+        <v>0.6095493747103341</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.0411692171706964</v>
+        <v>-0.9981366350124444</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8088</v>
+        <v>8081</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>441.5422885216645</v>
+        <v>446.2790107926707</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>45.15</v>
+        <v>233.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>26.32429958416314</v>
+        <v>28.96192247879989</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>23.11453978137643</v>
+        <v>29.60056532615773</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.3483616074326822</v>
+        <v>0.5443744957123356</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-1.692219740564488</v>
+        <v>-9.497274653187072</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2435,21 +2435,21 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8114</v>
+        <v>8102</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>434.5480142460482</v>
+        <v>445.0439504553092</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>183</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>36.794794519849</v>
+        <v>53.1024251651211</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>16.48753147662475</v>
+        <v>16.88612787101469</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.6250545271721283</v>
+        <v>0.6139064712739905</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.8966188293752548</v>
+        <v>0.4824865957975249</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8488</v>
+        <v>8067</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>431.608590955361</v>
+        <v>443.309956566461</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>10.25</v>
+        <v>13.45</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>52.13779427754898</v>
+        <v>52.43430812175527</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>11.96879764704019</v>
+        <v>4.898404389446418</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.2930866993001373</v>
+        <v>0.1045182362547632</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.08709996149523069</v>
+        <v>-0.0411692171706964</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8105</v>
+        <v>8088</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>428.6634087928583</v>
+        <v>441.5422885216645</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>16.05</v>
+        <v>45.15</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>31.18959459236345</v>
+        <v>26.32429958416314</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>30.04267107656997</v>
+        <v>23.11453978137643</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.3569474641568532</v>
+        <v>0.3483616074326822</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.778440624760055</v>
+        <v>-1.692219740564488</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2594,21 +2594,21 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8443</v>
+        <v>8114</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>428.3826625847399</v>
+        <v>434.5480142460482</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>11.4</v>
+        <v>183</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>47.76641216413745</v>
+        <v>36.794794519849</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>47.94406400585044</v>
+        <v>16.48753147662475</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.0859678688462267</v>
+        <v>0.6250545271721283</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.0068744718682293</v>
+        <v>-0.8966188293752548</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8093</v>
+        <v>8488</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>425.687139088977</v>
+        <v>431.608590955361</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>20.25</v>
+        <v>10.25</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>54.03628635106248</v>
+        <v>52.13779427754898</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>10.01049095626087</v>
+        <v>11.96879764704019</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.847939540564822</v>
+        <v>0.2930866993001373</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.0494384880262068</v>
+        <v>0.08709996149523069</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8932</v>
+        <v>8105</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>419.9999206235317</v>
+        <v>428.6634087928583</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>116.5</v>
+        <v>16.05</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>54.85651615066576</v>
+        <v>31.18959459236345</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>28.9649518464179</v>
+        <v>30.04267107656997</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.9738882664716492</v>
+        <v>0.3569474641568532</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.4255538249735213</v>
+        <v>-0.778440624760055</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8404</v>
+        <v>8443</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>419.6364530386554</v>
+        <v>428.3826625847399</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>16.9</v>
+        <v>11.4</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>51.52500370232336</v>
+        <v>47.76641216413745</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>21.15934974670169</v>
+        <v>47.94406400585044</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.7472917366166879</v>
+        <v>0.0859678688462267</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.0402953778986436</v>
+        <v>-0.0068744718682293</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>9907</v>
+        <v>8093</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>統一實</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>417.7462898329565</v>
+        <v>425.687139088977</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>15.1</v>
+        <v>20.25</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>38.69628937730637</v>
+        <v>54.03628635106248</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>25.79256769117899</v>
+        <v>10.01049095626087</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.9126202296479836</v>
+        <v>0.847939540564822</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.0277267338165843</v>
+        <v>-0.0494384880262068</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8481</v>
+        <v>8932</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>417.3959186445208</v>
+        <v>419.9999206235317</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>39.9</v>
+        <v>116.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>35.29199591567179</v>
+        <v>54.85651615066576</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>18.00055341762568</v>
+        <v>28.9649518464179</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>2.187549494704815</v>
+        <v>0.9738882664716492</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.1399420733690634</v>
+        <v>0.4255538249735213</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>9103</v>
+        <v>8404</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>415.3887674655189</v>
+        <v>419.6364530386554</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>5.18</v>
+        <v>16.9</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>49.80964395169408</v>
+        <v>51.52500370232336</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>14.03008203023474</v>
+        <v>21.15934974670169</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>3.111695686154587</v>
+        <v>0.7472917366166879</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.009316664631193799</v>
+        <v>0.0402953778986436</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8466</v>
+        <v>9907</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>統一實</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>403.0668766798765</v>
+        <v>417.7462898329565</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>17</v>
+        <v>15.1</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>52.88296726561042</v>
+        <v>38.69628937730637</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>26.53599781038028</v>
+        <v>25.79256769117899</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.228763885152016</v>
+        <v>0.9126202296479836</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.0268458418497593</v>
+        <v>0.0277267338165843</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8240</v>
+        <v>8481</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>399.1541443836308</v>
+        <v>417.3959186445208</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>42.3</v>
+        <v>39.9</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>25.70375454447681</v>
+        <v>35.29199591567179</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>26.67400123550372</v>
+        <v>18.00055341762568</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.6752034373823755</v>
+        <v>2.187549494704815</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.5696459004421071</v>
+        <v>-0.1399420733690634</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8390</v>
+        <v>9103</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>396.9511371523531</v>
+        <v>415.3887674655189</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>92.7</v>
+        <v>5.18</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>30.43002910719396</v>
+        <v>49.80964395169408</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>25.58474094037516</v>
+        <v>14.03008203023474</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.7274837884536933</v>
+        <v>3.111695686154587</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-1.125129434045745</v>
+        <v>0.009316664631193799</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8442</v>
+        <v>8466</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>396.9309693960192</v>
+        <v>403.0668766798765</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>44.85</v>
+        <v>17</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>57.18983204623247</v>
+        <v>52.88296726561042</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>40.21528188753313</v>
+        <v>26.53599781038028</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.5252460518155708</v>
+        <v>1.228763885152016</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.339268289812183</v>
+        <v>-0.0268458418497593</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8103</v>
+        <v>8240</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>392.6372218157684</v>
+        <v>399.1541443836308</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>76.5</v>
+        <v>42.3</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>28.25712183702805</v>
+        <v>25.70375454447681</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>25.56431101271168</v>
+        <v>26.67400123550372</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.9196373900894168</v>
+        <v>0.6752034373823755</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-2.068449098493354</v>
+        <v>-0.5696459004421071</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8210</v>
+        <v>8390</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>391.6527723729646</v>
+        <v>396.9511371523531</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>1080</v>
+        <v>92.7</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>34.10292046191579</v>
+        <v>30.43002910719396</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>24.76514248529373</v>
+        <v>25.58474094037516</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.056263813158627</v>
+        <v>0.7274837884536933</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-14.96222174670356</v>
+        <v>-1.125129434045745</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8926</v>
+        <v>8442</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>391.5444931199427</v>
+        <v>396.9309693960192</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>64</v>
+        <v>44.85</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>36.02165341104256</v>
+        <v>57.18983204623247</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>30.45440518229228</v>
+        <v>40.21528188753313</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.5219149710283467</v>
+        <v>0.5252460518155708</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-1.980820685541556</v>
+        <v>0.339268289812183</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8299</v>
+        <v>8103</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>391.5089695110924</v>
+        <v>392.6372218157684</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>1735</v>
+        <v>76.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,49 +3361,49 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>30.06317615337719</v>
+        <v>28.25712183702805</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>18.18861078388955</v>
+        <v>25.56431101271168</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.932473476898944</v>
+        <v>0.9196373900894168</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-54.29047887672566</v>
+        <v>-2.068449098493354</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8111</v>
+        <v>8210</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>387.0840233074269</v>
+        <v>391.6527723729646</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>44.25</v>
+        <v>1080</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>28.61317760324311</v>
+        <v>34.10292046191579</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>25.96229385432875</v>
+        <v>24.76514248529373</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>3.047241785468709</v>
+        <v>1.056263813158627</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.1620223325223877</v>
+        <v>-14.96222174670356</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8478</v>
+        <v>8926</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>385.2129909884111</v>
+        <v>391.5444931199427</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>43.86285700565237</v>
+        <v>36.02165341104256</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>15.32499458363431</v>
+        <v>30.45440518229228</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.6885914757842072</v>
+        <v>0.5219149710283467</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.2555169162460702</v>
+        <v>-1.980820685541556</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8213</v>
+        <v>8299</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>383.7044859804673</v>
+        <v>391.5089695110924</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>30.9</v>
+        <v>1735</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,49 +3520,49 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>27.37966965774872</v>
+        <v>30.06317615337719</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>23.87415504800938</v>
+        <v>18.18861078388955</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.506563416810919</v>
+        <v>0.932473476898944</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.3474032863928936</v>
+        <v>-54.29047887672566</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8215</v>
+        <v>8111</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>382.3595803803656</v>
+        <v>387.0840233074269</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>24.45</v>
+        <v>44.25</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>34.43342584066329</v>
+        <v>28.61317760324311</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>20.03697505022785</v>
+        <v>25.96229385432875</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.6050558896768479</v>
+        <v>3.047241785468709</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.5188979594588511</v>
+        <v>-0.1620223325223877</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>9910</v>
+        <v>8478</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>380.867973185235</v>
+        <v>385.2129909884111</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>68.2</v>
+        <v>151</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>44.02304682233773</v>
+        <v>43.86285700565237</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>16.86098544840586</v>
+        <v>15.32499458363431</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.143655668211836</v>
+        <v>0.6885914757842072</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.060507039841724</v>
+        <v>-0.2555169162460702</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>9905</v>
+        <v>8213</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>371.9604810088805</v>
+        <v>383.7044859804673</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>20.6</v>
+        <v>30.9</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>41.46795162260218</v>
+        <v>27.37966965774872</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>24.6504478493708</v>
+        <v>23.87415504800938</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.5468842479073307</v>
+        <v>1.506563416810919</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.0617490947930138</v>
+        <v>-0.3474032863928936</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8147</v>
+        <v>8215</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>371.4412692109866</v>
+        <v>382.3595803803656</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>128.5</v>
+        <v>24.45</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>32.10143898896499</v>
+        <v>34.43342584066329</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>19.50159949926803</v>
+        <v>20.03697505022785</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.8396317699788701</v>
+        <v>0.6050558896768479</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-1.513826687986452</v>
+        <v>-0.5188979594588511</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8473</v>
+        <v>9910</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>370.551438742452</v>
+        <v>380.867973185235</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>43.6</v>
+        <v>68.2</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>39.56678661601394</v>
+        <v>44.02304682233773</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>20.88473370305333</v>
+        <v>16.86098544840586</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.6154875724752006</v>
+        <v>1.143655668211836</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.6026848848676558</v>
+        <v>0.060507039841724</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8104</v>
+        <v>9905</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>370.5313889011292</v>
+        <v>371.9604810088805</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>33.45</v>
+        <v>20.6</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>33.84494711728198</v>
+        <v>41.46795162260218</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>19.2174582572087</v>
+        <v>24.6504478493708</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.1752724531114093</v>
+        <v>0.5468842479073307</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.710071202879317</v>
+        <v>-0.0617490947930138</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8131</v>
+        <v>8147</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>366.1031628205109</v>
+        <v>371.4412692109866</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>67.2</v>
+        <v>128.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>42.53812631923978</v>
+        <v>32.10143898896499</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>14.2167833902899</v>
+        <v>19.50159949926803</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.5919251658459365</v>
+        <v>0.8396317699788701</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.9503626830599488</v>
+        <v>-1.513826687986452</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3919,21 +3919,21 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8070</v>
+        <v>8473</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>364.5296055858848</v>
+        <v>370.551438742452</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>46.7</v>
+        <v>43.6</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>34.11477759672619</v>
+        <v>39.56678661601394</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>19.6807319439278</v>
+        <v>20.88473370305333</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.4595675981768153</v>
+        <v>0.6154875724752006</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.9718601634583094</v>
+        <v>-0.6026848848676558</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8162</v>
+        <v>8104</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>357.1616873090703</v>
+        <v>370.5313889011292</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>61</v>
+        <v>33.45</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>35.1432591700255</v>
+        <v>33.84494711728198</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>28.49995854880677</v>
+        <v>19.2174582572087</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.8739397595613534</v>
+        <v>0.1752724531114093</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-2.492693204474112</v>
+        <v>-0.710071202879317</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8454</v>
+        <v>8131</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>348.5473726580755</v>
+        <v>366.1031628205109</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>253.5</v>
+        <v>67.2</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>39.1128745100719</v>
+        <v>42.53812631923978</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>21.0925851145632</v>
+        <v>14.2167833902899</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.4595708579249234</v>
+        <v>0.5919251658459365</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-6.13663560599683</v>
+        <v>-0.9503626830599488</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8171</v>
+        <v>8070</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>329.6827708892724</v>
+        <v>364.5296055858848</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>20.8</v>
+        <v>46.7</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>45.47093543346924</v>
+        <v>34.11477759672619</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>16.02879174126203</v>
+        <v>19.6807319439278</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.426555995942424</v>
+        <v>0.4595675981768153</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.0460329632027097</v>
+        <v>-0.9718601634583094</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8455</v>
+        <v>8162</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>326.4367736786218</v>
+        <v>357.1616873090703</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>24.8</v>
+        <v>61</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>38.01252615331278</v>
+        <v>35.1432591700255</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>20.00997350193153</v>
+        <v>28.49995854880677</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.2690118165304508</v>
+        <v>0.8739397595613534</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.1010393676820735</v>
+        <v>-2.492693204474112</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8499</v>
+        <v>8454</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>313.2499384843146</v>
+        <v>348.5473726580755</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>269</v>
+        <v>253.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>39.82529025363888</v>
+        <v>39.1128745100719</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>13.00803913955954</v>
+        <v>21.0925851145632</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.8251925838420565</v>
+        <v>0.4595708579249234</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-4.033523828536281</v>
+        <v>-6.13663560599683</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8048</v>
+        <v>8171</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>308.0845245425451</v>
+        <v>329.6827708892724</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>55.1</v>
+        <v>20.8</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>31.01381501673919</v>
+        <v>45.47093543346924</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>17.29416403681101</v>
+        <v>16.02879174126203</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.7677368775004803</v>
+        <v>1.426555995942424</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.6899268082477932</v>
+        <v>0.0460329632027097</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8068</v>
+        <v>8455</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>307.8659465645239</v>
+        <v>326.4367736786218</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>18.65</v>
+        <v>24.8</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>45.79139577858005</v>
+        <v>38.01252615331278</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>14.67766659627077</v>
+        <v>20.00997350193153</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.6718612756214281</v>
+        <v>0.2690118165304508</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.06479370212465869</v>
+        <v>-0.1010393676820735</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8112</v>
+        <v>8499</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>307.5614430210653</v>
+        <v>313.2499384843146</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>80.90000000000001</v>
+        <v>269</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>36.50382439332736</v>
+        <v>39.82529025363888</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>13.86342463770381</v>
+        <v>13.00803913955954</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.4765246916139745</v>
+        <v>0.8251925838420565</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-1.103514483333838</v>
+        <v>-4.033523828536281</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8084</v>
+        <v>8048</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>304.9100718020537</v>
+        <v>308.0845245425451</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>45.9</v>
+        <v>55.1</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>44.55007495948547</v>
+        <v>31.01381501673919</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>18.23970962719124</v>
+        <v>17.29416403681101</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.285143900641639</v>
+        <v>0.7677368775004803</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.4825051804052064</v>
+        <v>-0.6899268082477932</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8054</v>
+        <v>8068</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>302.8679607375613</v>
+        <v>307.8659465645239</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>88.7</v>
+        <v>18.65</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>33.11140364823417</v>
+        <v>45.79139577858005</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>21.38940382089634</v>
+        <v>14.67766659627077</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.3418680353264094</v>
+        <v>0.6718612756214281</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>1</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-2.615352357902281</v>
+        <v>0.06479370212465869</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8076</v>
+        <v>8112</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>301.8782472567674</v>
+        <v>307.5614430210653</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>23</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>35.6274094855786</v>
+        <v>36.50382439332736</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>14.86153701221526</v>
+        <v>13.86342463770381</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.8250819085629445</v>
+        <v>0.4765246916139745</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.3193765140112602</v>
+        <v>-1.103514483333838</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8110</v>
+        <v>8084</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>296.687932383126</v>
+        <v>304.9100718020537</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>41.15</v>
+        <v>45.9</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>30.43027407429412</v>
+        <v>44.55007495948547</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>18.0208220572255</v>
+        <v>18.23970962719124</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.4010568826924436</v>
+        <v>1.285143900641639</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-1.342778156524591</v>
+        <v>-0.4825051804052064</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>9955</v>
+        <v>8054</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>284.6319684910669</v>
+        <v>302.8679607375613</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>23.9</v>
+        <v>88.7</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>28.68050111870811</v>
+        <v>33.11140364823417</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>27.72678864925133</v>
+        <v>21.38940382089634</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.9082348740622485</v>
+        <v>0.3418680353264094</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.1956309830826477</v>
+        <v>-2.615352357902281</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>9930</v>
+        <v>8076</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>282.7184209014969</v>
+        <v>301.8782472567674</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>63.4</v>
+        <v>23</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>31.26732270092597</v>
+        <v>35.6274094855786</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>49.39235385112368</v>
+        <v>14.86153701221526</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.005015203371471</v>
+        <v>0.8250819085629445</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.0597080058363528</v>
+        <v>-0.3193765140112602</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>9904</v>
+        <v>8110</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>270.8919014662148</v>
+        <v>296.687932383126</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>24.35</v>
+        <v>41.15</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>37.27404920859792</v>
+        <v>30.43027407429412</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>21.06008365170581</v>
+        <v>18.0208220572255</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.8739171897574929</v>
+        <v>0.4010568826924436</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0191894324978431</v>
+        <v>-1.342778156524591</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>9136</v>
+        <v>9955</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>270.5244213656657</v>
+        <v>284.6319684910669</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>11.6</v>
+        <v>23.9</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>36.40408603739359</v>
+        <v>28.68050111870811</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>22.36783253435512</v>
+        <v>27.72678864925133</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.5748244585714913</v>
+        <v>0.9082348740622485</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.4024049927445913</v>
+        <v>-0.1956309830826477</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>9906</v>
+        <v>9930</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>欣巴巴</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>262.5202745230274</v>
+        <v>282.7184209014969</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>39.5</v>
+        <v>63.4</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>43.34316858927606</v>
+        <v>31.26732270092597</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>22.25499412917491</v>
+        <v>49.39235385112368</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.5228303365349617</v>
+        <v>1.005015203371471</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.3365621385625379</v>
+        <v>-0.0597080058363528</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8089</v>
+        <v>9904</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>259.2127133125301</v>
+        <v>270.8919014662148</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>18.35</v>
+        <v>24.35</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>34.18675576529442</v>
+        <v>37.27404920859792</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>23.78599275700904</v>
+        <v>21.06008365170581</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.8213629712374783</v>
+        <v>0.8739171897574929</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.1985568325541248</v>
+        <v>0.0191894324978431</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8059</v>
+        <v>9136</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>255.56495457672</v>
+        <v>270.5244213656657</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>15.5</v>
+        <v>11.6</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>36.58240758093697</v>
+        <v>36.40408603739359</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>22.53974317663304</v>
+        <v>22.36783253435512</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.7307042930808083</v>
+        <v>0.5748244585714913</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0282820326562579</v>
+        <v>-0.4024049927445913</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8277</v>
+        <v>9906</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>欣巴巴</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>251.8677941489803</v>
+        <v>262.5202745230274</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>7.9</v>
+        <v>39.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>34.86523198529916</v>
+        <v>43.34316858927606</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>23.82878496272343</v>
+        <v>22.25499412917491</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.7380507563177565</v>
+        <v>0.5228303365349617</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.1804472055182256</v>
+        <v>-0.3365621385625379</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8249</v>
+        <v>8089</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>250.184248058025</v>
+        <v>259.2127133125301</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>43.65</v>
+        <v>18.35</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>28.86300397807922</v>
+        <v>34.18675576529442</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>15.29717312444641</v>
+        <v>23.78599275700904</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.7080640616967376</v>
+        <v>0.8213629712374783</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.3165110807344926</v>
+        <v>-0.1985568325541248</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8201</v>
+        <v>8059</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>245.7756666515316</v>
+        <v>255.56495457672</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>12.4</v>
+        <v>15.5</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>41.38763310976477</v>
+        <v>36.58240758093697</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>13.73004326193214</v>
+        <v>22.53974317663304</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5731632948891828</v>
+        <v>0.7307042930808083</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0675880235671633</v>
+        <v>0.0282820326562579</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8477</v>
+        <v>8277</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>244.28268969514</v>
+        <v>251.8677941489803</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>15.2</v>
+        <v>7.9</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>37.15242913059014</v>
+        <v>34.86523198529916</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>12.7680764896199</v>
+        <v>23.82878496272343</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.6625162782319926</v>
+        <v>0.7380507563177565</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.1009739330615715</v>
+        <v>-0.1804472055182256</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8087</v>
+        <v>8249</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>241.0065654995698</v>
+        <v>250.184248058025</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>26.9</v>
+        <v>43.65</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>25.46595760514008</v>
+        <v>28.86300397807922</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>16.18086017138939</v>
+        <v>15.29717312444641</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.156425018073055</v>
+        <v>0.7080640616967376</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.5132972520617309</v>
+        <v>-0.3165110807344926</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>9802</v>
+        <v>8201</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>240.6913550792188</v>
+        <v>245.7756666515316</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>74.2</v>
+        <v>12.4</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>47.10174050488181</v>
+        <v>41.38763310976477</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>10.91062775433359</v>
+        <v>13.73004326193214</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.059356319899883</v>
+        <v>0.5731632948891828</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.1961566054608634</v>
+        <v>-0.0675880235671633</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8422</v>
+        <v>8477</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>232.9108317933049</v>
+        <v>244.28268969514</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>25.8</v>
+        <v>15.2</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>38.85316261472667</v>
+        <v>37.15242913059014</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>14.13871027061122</v>
+        <v>12.7680764896199</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.6075310050878462</v>
+        <v>0.6625162782319926</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.1963960587337506</v>
+        <v>-0.1009739330615715</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8049</v>
+        <v>8087</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>229.9267764203604</v>
+        <v>241.0065654995698</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>25.7</v>
+        <v>26.9</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>35.58755997224677</v>
+        <v>25.46595760514008</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>18.59637131813364</v>
+        <v>16.18086017138939</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.324695904726914</v>
+        <v>0.156425018073055</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.1781314722737861</v>
+        <v>-0.5132972520617309</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8080</v>
+        <v>9802</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>223.8960621654276</v>
+        <v>240.6913550792188</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>26.8</v>
+        <v>74.2</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>35.9121572255637</v>
+        <v>47.10174050488181</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>38.00115857352466</v>
+        <v>10.91062775433359</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.9203430860261228</v>
+        <v>1.059356319899883</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.0973394851735931</v>
+        <v>0.1961566054608634</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8940</v>
+        <v>8422</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>216.3128689736374</v>
+        <v>232.9108317933049</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>16</v>
+        <v>25.8</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>36.38263723439968</v>
+        <v>38.85316261472667</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>17.48849525321772</v>
+        <v>14.13871027061122</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.507056933722115</v>
+        <v>0.6075310050878462</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.0322670438855249</v>
+        <v>-0.1963960587337506</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8085</v>
+        <v>8049</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>197.7041179947152</v>
+        <v>229.9267764203604</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>11.1</v>
+        <v>25.7</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>36.81115584141291</v>
+        <v>35.58755997224677</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>22.59991097317074</v>
+        <v>18.59637131813364</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.191878751727309</v>
+        <v>0.324695904726914</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0790472104120981</v>
+        <v>-0.1781314722737861</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8467</v>
+        <v>8080</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>196.3552880798136</v>
+        <v>223.8960621654276</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>102</v>
+        <v>26.8</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>41.26604211808932</v>
+        <v>35.9121572255637</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>13.05592819492755</v>
+        <v>38.00115857352466</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>2.048543243394965</v>
+        <v>0.9203430860261228</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.7508451126360054</v>
+        <v>-0.0973394851735931</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8101</v>
+        <v>8940</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>194.3726177002769</v>
+        <v>216.3128689736374</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>13.4</v>
+        <v>16</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>47.39393727759823</v>
+        <v>36.38263723439968</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>11.14719740896459</v>
+        <v>17.48849525321772</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.0425528979158186</v>
+        <v>1.507056933722115</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.032941830326481</v>
+        <v>-0.0322670438855249</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8431</v>
+        <v>8085</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>189.2899849465213</v>
+        <v>197.7041179947152</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>46.3</v>
+        <v>11.1</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>36.02225200507795</v>
+        <v>36.81115584141291</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>17.66064641299849</v>
+        <v>22.59991097317074</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.325253676585173</v>
+        <v>1.191878751727309</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.4519823104303437</v>
+        <v>-0.0790472104120981</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8423</v>
+        <v>8467</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>177.4177457419045</v>
+        <v>196.3552880798136</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>17.55</v>
+        <v>102</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>44.02654173872418</v>
+        <v>41.26604211808932</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>9.966779050265837</v>
+        <v>13.05592819492755</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.017594379447594</v>
+        <v>2.048543243394965</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.009489144294095401</v>
+        <v>-0.7508451126360054</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8429</v>
+        <v>8101</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>176.3200114523451</v>
+        <v>194.3726177002769</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>6.08</v>
+        <v>13.4</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>36.33121305975095</v>
+        <v>47.39393727759823</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>12.93598942566858</v>
+        <v>11.14719740896459</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.8856939788638886</v>
+        <v>0.0425528979158186</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.0168570982406815</v>
+        <v>0.032941830326481</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8072</v>
+        <v>8431</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>176.1764806657739</v>
+        <v>189.2899849465213</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>26.75</v>
+        <v>46.3</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>36.86901990437292</v>
+        <v>36.02225200507795</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>17.46023508697142</v>
+        <v>17.66064641299849</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.7202081239793905</v>
+        <v>1.325253676585173</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.296945740883049</v>
+        <v>-0.4519823104303437</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8097</v>
+        <v>8423</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>174.4657915583758</v>
+        <v>177.4177457419045</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>52.3</v>
+        <v>17.55</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>28.03220428245525</v>
+        <v>44.02654173872418</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>14.85774083928837</v>
+        <v>9.966779050265837</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.9352158843810416</v>
+        <v>1.017594379447594</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.693608023300517</v>
+        <v>-0.009489144294095401</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5933,21 +5933,21 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8440</v>
+        <v>8429</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>172.5731781963395</v>
+        <v>176.3200114523451</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>20.2</v>
+        <v>6.08</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>32.59528265900835</v>
+        <v>36.33121305975095</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>13.0946665740224</v>
+        <v>12.93598942566858</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.264666562534456</v>
+        <v>0.8856939788638886</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.0913667907137545</v>
+        <v>-0.0168570982406815</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>9110</v>
+        <v>8072</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>171.0164501739962</v>
+        <v>176.1764806657739</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>3.11</v>
+        <v>26.75</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>50.3337572909</v>
+        <v>36.86901990437292</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>8.117771399087831</v>
+        <v>17.46023508697142</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.5083069078908783</v>
+        <v>0.7202081239793905</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.0069308246299152</v>
+        <v>-0.296945740883049</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8092</v>
+        <v>8097</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>170.6210508679903</v>
+        <v>174.4657915583758</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>13.6</v>
+        <v>52.3</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>38.70978932843306</v>
+        <v>28.03220428245525</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>15.31931610404829</v>
+        <v>14.85774083928837</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.5487023894852511</v>
+        <v>0.9352158843810416</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0621326681725789</v>
+        <v>-0.693608023300517</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8487</v>
+        <v>8440</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>156.8655511834135</v>
+        <v>172.5731781963395</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>75.09999999999999</v>
+        <v>20.2</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>36.05327811354281</v>
+        <v>32.59528265900835</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>15.50556710526754</v>
+        <v>13.0946665740224</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.31406341178759</v>
+        <v>1.264666562534456</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.2388397380193867</v>
+        <v>-0.0913667907137545</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8176</v>
+        <v>9110</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>152.3765253416069</v>
+        <v>171.0164501739962</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>9.880000000000001</v>
+        <v>3.11</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>41.35435942243586</v>
+        <v>50.3337572909</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>17.30522010527877</v>
+        <v>8.117771399087831</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.3250477309106204</v>
+        <v>0.5083069078908783</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0513693896559195</v>
+        <v>0.0069308246299152</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>9902</v>
+        <v>8092</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>150.8380156277368</v>
+        <v>170.6210508679903</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>43.67564198279485</v>
+        <v>38.70978932843306</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>13.72156113514578</v>
+        <v>15.31931610404829</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.711596187312217</v>
+        <v>0.5487023894852511</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0143488061619763</v>
+        <v>0.0621326681725789</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8472</v>
+        <v>8487</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>139.2346234463888</v>
+        <v>156.8655511834135</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>78.59999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>43.93449157166249</v>
+        <v>36.05327811354281</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>12.25263913518639</v>
+        <v>15.50556710526754</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.160336536759134</v>
+        <v>1.31406341178759</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.5856418818821031</v>
+        <v>-0.2388397380193867</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>9911</v>
+        <v>8176</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>櫻花</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>136.4442926488551</v>
+        <v>152.3765253416069</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>83.2</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>46.73430623279845</v>
+        <v>41.35435942243586</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>11.79150516091568</v>
+        <v>17.30522010527877</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.384657436864264</v>
+        <v>0.3250477309106204</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0445499223591432</v>
+        <v>-0.0513693896559195</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8341</v>
+        <v>9902</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>117.9303133818338</v>
+        <v>150.8380156277368</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>75.90000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>43.30417074962944</v>
+        <v>43.67564198279485</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>15.31136669498757</v>
+        <v>13.72156113514578</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.7220196667050502</v>
+        <v>0.711596187312217</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0921787773446127</v>
+        <v>-0.0143488061619763</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6410,21 +6410,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8410</v>
+        <v>8472</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>108.4340665790842</v>
+        <v>139.2346234463888</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>31.4</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>30.11618886536186</v>
+        <v>43.93449157166249</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>16.51060530185221</v>
+        <v>12.25263913518639</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.8182063485462331</v>
+        <v>0.160336536759134</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,62 +6453,221 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0421977468182216</v>
+        <v>-0.5856418818821031</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
+        <v>9911</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>櫻花</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>136.4442926488551</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>46.73430623279845</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>11.79150516091568</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>1.384657436864264</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>-0.0445499223591432</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>8341</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>日友</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>117.9303133818338</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>43.30417074962944</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>15.31136669498757</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.7220196667050502</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>-0.0921787773446127</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>8410</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>森田</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>108.4340665790842</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>30.11618886536186</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>16.51060530185221</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.8182063485462331</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>-0.0421977468182216</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
         <v>8463</v>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>潤泰材</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D114" s="2" t="n">
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
         <v>62.28934733448898</v>
       </c>
-      <c r="E114" s="2" t="n">
+      <c r="E117" s="2" t="n">
         <v>21.3</v>
       </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H114" s="2" t="n">
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
         <v>43.96683941560782</v>
       </c>
-      <c r="I114" s="2" t="n">
+      <c r="I117" s="2" t="n">
         <v>10.32236366802521</v>
       </c>
-      <c r="J114" s="2" t="n">
+      <c r="J117" s="2" t="n">
         <v>1.040546901701477</v>
       </c>
-      <c r="K114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M114" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N114" s="2" t="n">
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
         <v>0.0149934062470724</v>
       </c>
-      <c r="O114" s="2" t="inlineStr">
+      <c r="O117" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>

--- a/output/full_scan/batch_seq0_2026-07-20.xlsx
+++ b/output/full_scan/batch_seq0_2026-07-20.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O117"/>
+  <dimension ref="A1:O118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1004,21 +1004,21 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8411</v>
+        <v>8261</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>544.7843101201854</v>
+        <v>560.0126071674899</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>12.6</v>
+        <v>229</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,49 +1029,49 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>61.05090394543221</v>
+        <v>42.5703835812243</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>20.7988837358909</v>
+        <v>41.52718011613792</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.5688712337875449</v>
+        <v>0.2200840863377934</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.0332744926036658</v>
+        <v>-12.72945774870873</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8050</v>
+        <v>8411</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>543.8089052891864</v>
+        <v>544.7843101201854</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>55.6</v>
+        <v>12.6</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>47.41337549136543</v>
+        <v>61.05090394543221</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>25.50821236064068</v>
+        <v>20.7988837358909</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.9681053917473508</v>
+        <v>0.5688712337875449</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.0502230215828642</v>
+        <v>0.0332744926036658</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8438</v>
+        <v>8050</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>538.1280823870151</v>
+        <v>543.8089052891864</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>71.09999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>29.26113520221377</v>
+        <v>47.41337549136543</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>25.82997947844575</v>
+        <v>25.50821236064068</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.456817914136796</v>
+        <v>0.9681053917473508</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-2.985334002173479</v>
+        <v>-0.0502230215828642</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8476</v>
+        <v>8438</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>535.2277799674955</v>
+        <v>538.1280823870151</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>24.35</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>64.4889547275572</v>
+        <v>29.26113520221377</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>39.24368613637008</v>
+        <v>25.82997947844575</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.6823670038997799</v>
+        <v>2.456817914136796</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.2181426586709516</v>
+        <v>-2.985334002173479</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8996</v>
+        <v>8476</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>529.4329150217334</v>
+        <v>535.2277799674955</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>971</v>
+        <v>24.35</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>31.61825428526758</v>
+        <v>64.4889547275572</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>23.19446785403177</v>
+        <v>39.24368613637008</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2.378840215057157</v>
+        <v>0.6823670038997799</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-56.12320165194066</v>
+        <v>-0.2181426586709516</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>9912</v>
+        <v>8996</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>521.4114569242587</v>
+        <v>529.4329150217334</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>12.6</v>
+        <v>971</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>50.22345738834519</v>
+        <v>31.61825428526758</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>18.16604411827472</v>
+        <v>23.19446785403177</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.2055904027789353</v>
+        <v>2.378840215057157</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.0022878288788672</v>
+        <v>-56.12320165194066</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8464</v>
+        <v>9912</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>519.9023864328175</v>
+        <v>521.4114569242587</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>360</v>
+        <v>12.6</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>53.7464431493932</v>
+        <v>50.22345738834519</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>24.78224988608148</v>
+        <v>18.16604411827472</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.9197641759172968</v>
+        <v>0.2055904027789353</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-1.345887768581846</v>
+        <v>-0.0022878288788672</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8182</v>
+        <v>8464</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>515.8127775889877</v>
+        <v>519.9023864328175</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>39.7</v>
+        <v>360</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>37.41032868653702</v>
+        <v>53.7464431493932</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>21.2500521241284</v>
+        <v>24.78224988608148</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.2034041549150358</v>
+        <v>0.9197641759172968</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-1.704560270827079</v>
+        <v>-1.345887768581846</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8271</v>
+        <v>8182</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>502.1141714103779</v>
+        <v>515.8127775889877</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>184</v>
+        <v>39.7</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>42.58524625652541</v>
+        <v>37.41032868653702</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>24.27960979013329</v>
+        <v>21.2500521241284</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.384325680930195</v>
+        <v>0.2034041549150358</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.7486613957583117</v>
+        <v>-1.704560270827079</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8482</v>
+        <v>8271</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>491.6032578339965</v>
+        <v>502.1141714103779</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>48.75</v>
+        <v>184</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>51.7543539425529</v>
+        <v>42.58524625652541</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>4.957580825594084</v>
+        <v>24.27960979013329</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>3.01531319165782</v>
+        <v>1.384325680930195</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.5559110662961007</v>
+        <v>0.7486613957583117</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8183</v>
+        <v>8482</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>491.5665803592696</v>
+        <v>491.6032578339965</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>30</v>
+        <v>48.75</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>36.56656772336066</v>
+        <v>51.7543539425529</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>23.5370900151153</v>
+        <v>4.957580825594084</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.4679446573358414</v>
+        <v>3.01531319165782</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.462545128125255</v>
+        <v>0.5559110662961007</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8358</v>
+        <v>8183</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>482.8252271388071</v>
+        <v>491.5665803592696</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>371</v>
+        <v>30</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,49 +1612,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>27.90431223654707</v>
+        <v>36.56656772336066</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>17.96011505973614</v>
+        <v>23.5370900151153</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.7189089305518133</v>
+        <v>0.4679446573358414</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-23.60176628451044</v>
+        <v>-0.462545128125255</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8074</v>
+        <v>8358</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>475.9522450423017</v>
+        <v>482.8252271388071</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>53.7</v>
+        <v>371</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,49 +1665,49 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>27.48885430352295</v>
+        <v>27.90431223654707</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>27.39091018765874</v>
+        <v>17.96011505973614</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.8414725066825216</v>
+        <v>0.7189089305518133</v>
       </c>
       <c r="K23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-1.135340347635904</v>
+        <v>-23.60176628451044</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8234</v>
+        <v>8074</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>473.2163611007624</v>
+        <v>475.9522450423017</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>58.7</v>
+        <v>53.7</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>35.80936045123424</v>
+        <v>27.48885430352295</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>22.31134913511922</v>
+        <v>27.39091018765874</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.4528140258123299</v>
+        <v>0.8414725066825216</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-1.126276195057965</v>
+        <v>-1.135340347635904</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8121</v>
+        <v>8234</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>472.8271411151015</v>
+        <v>473.2163611007624</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>33.8</v>
+        <v>58.7</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>31.01959071655206</v>
+        <v>35.80936045123424</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>25.79948406182832</v>
+        <v>22.31134913511922</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.6089438655896472</v>
+        <v>0.4528140258123299</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-1.769140250795477</v>
+        <v>-1.126276195057965</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8291</v>
+        <v>8121</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>470.7463275582508</v>
+        <v>472.8271411151015</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>33.05</v>
+        <v>33.8</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>40.82711779479388</v>
+        <v>31.01959071655206</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>31.88783227388325</v>
+        <v>25.79948406182832</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.1396337922733177</v>
+        <v>0.6089438655896472</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.1446950747342228</v>
+        <v>-1.769140250795477</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, hist_turn_positive, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8064</v>
+        <v>8291</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>470.6621589515572</v>
+        <v>470.7463275582508</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>108</v>
+        <v>33.05</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>34.62638224340604</v>
+        <v>40.82711779479388</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>16.95087664309198</v>
+        <v>31.88783227388325</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.7544964246122771</v>
+        <v>0.1396337922733177</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-3.592442841308582</v>
+        <v>0.1446950747342228</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8222</v>
+        <v>8064</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>463.1621837889962</v>
+        <v>470.6621589515572</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>37.8</v>
+        <v>108</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>46.91767791103925</v>
+        <v>34.62638224340604</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>27.24257552508554</v>
+        <v>16.95087664309198</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.9563125982760518</v>
+        <v>0.7544964246122771</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.3800918433855049</v>
+        <v>-3.592442841308582</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8227</v>
+        <v>8222</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>463.0937597040056</v>
+        <v>463.1621837889962</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>142.5</v>
+        <v>37.8</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>31.26528100458584</v>
+        <v>46.91767791103925</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>19.70404026439344</v>
+        <v>27.24257552508554</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.4401636614987188</v>
+        <v>0.9563125982760518</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-5.782000921745363</v>
+        <v>-0.3800918433855049</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>9908</v>
+        <v>8227</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>大台北</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>462.0842696738495</v>
+        <v>463.0937597040056</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>29.1</v>
+        <v>142.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>36.22165888787202</v>
+        <v>31.26528100458584</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>24.33206912351723</v>
+        <v>19.70404026439344</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.799767829613555</v>
+        <v>0.4401636614987188</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.09436723757039529</v>
+        <v>-5.782000921745363</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8096</v>
+        <v>9908</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>大台北</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>461.9968365404445</v>
+        <v>462.0842696738495</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>128</v>
+        <v>29.1</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>39.64939700254032</v>
+        <v>36.22165888787202</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>27.66239680319825</v>
+        <v>24.33206912351723</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.2851862420929087</v>
+        <v>1.799767829613555</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-4.970931627071428</v>
+        <v>-0.09436723757039529</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8086</v>
+        <v>8096</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>461.0828955572761</v>
+        <v>461.9968365404445</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>28.37874684555842</v>
+        <v>39.64939700254032</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>22.11089860590064</v>
+        <v>27.66239680319825</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.8669990470277117</v>
+        <v>0.2851862420929087</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-2.595418119352227</v>
+        <v>-4.970931627071428</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8163</v>
+        <v>8086</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>454.644685378633</v>
+        <v>461.0828955572761</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>32.5</v>
+        <v>115</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>32.99370978676362</v>
+        <v>28.37874684555842</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>25.44857883322119</v>
+        <v>22.11089860590064</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.5153588422073061</v>
+        <v>0.8669990470277117</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-1.073116841435888</v>
+        <v>-2.595418119352227</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2223,21 +2223,21 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>9105</v>
+        <v>8163</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>453.2626265858052</v>
+        <v>454.644685378633</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>8.43</v>
+        <v>32.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>42.31981542603865</v>
+        <v>32.99370978676362</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>20.5947634684721</v>
+        <v>25.44857883322119</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.6949963680965144</v>
+        <v>0.5153588422073061</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.1381093433188907</v>
+        <v>-1.073116841435888</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2276,21 +2276,21 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8069</v>
+        <v>9105</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>452.552231795313</v>
+        <v>453.2626265858052</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>175.5</v>
+        <v>8.43</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,49 +2301,49 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>33.39594313084636</v>
+        <v>42.31981542603865</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>15.81293042210594</v>
+        <v>20.5947634684721</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.7430510961542823</v>
+        <v>0.6949963680965144</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-3.020169442121304</v>
+        <v>-0.1381093433188907</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8374</v>
+        <v>8069</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>447.9414560005962</v>
+        <v>452.552231795313</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>75.8</v>
+        <v>175.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,49 +2354,49 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>32.91573495204673</v>
+        <v>33.39594313084636</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>13.25219277200956</v>
+        <v>15.81293042210594</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.6095493747103341</v>
+        <v>0.7430510961542823</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.9981366350124444</v>
+        <v>-3.020169442121304</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8081</v>
+        <v>8374</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>446.2790107926707</v>
+        <v>447.9414560005962</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>233.5</v>
+        <v>75.8</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>28.96192247879989</v>
+        <v>32.91573495204673</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>29.60056532615773</v>
+        <v>13.25219277200956</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.5443744957123356</v>
+        <v>0.6095493747103341</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-9.497274653187072</v>
+        <v>-0.9981366350124444</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8102</v>
+        <v>8081</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>445.0439504553092</v>
+        <v>446.2790107926707</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>72.09999999999999</v>
+        <v>233.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>53.1024251651211</v>
+        <v>28.96192247879989</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>16.88612787101469</v>
+        <v>29.60056532615773</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.6139064712739905</v>
+        <v>0.5443744957123356</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.4824865957975249</v>
+        <v>-9.497274653187072</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8067</v>
+        <v>8102</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>443.309956566461</v>
+        <v>445.0439504553092</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>13.45</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>52.43430812175527</v>
+        <v>53.1024251651211</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>4.898404389446418</v>
+        <v>16.88612787101469</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.1045182362547632</v>
+        <v>0.6139064712739905</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.0411692171706964</v>
+        <v>0.4824865957975249</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8088</v>
+        <v>8067</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>441.5422885216645</v>
+        <v>443.309956566461</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>45.15</v>
+        <v>13.45</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>26.32429958416314</v>
+        <v>52.43430812175527</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>23.11453978137643</v>
+        <v>4.898404389446418</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.3483616074326822</v>
+        <v>0.1045182362547632</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-1.692219740564488</v>
+        <v>-0.0411692171706964</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8114</v>
+        <v>8088</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>434.5480142460482</v>
+        <v>441.5422885216645</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>183</v>
+        <v>45.15</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>36.794794519849</v>
+        <v>26.32429958416314</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>16.48753147662475</v>
+        <v>23.11453978137643</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.6250545271721283</v>
+        <v>0.3483616074326822</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.8966188293752548</v>
+        <v>-1.692219740564488</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8488</v>
+        <v>8114</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>431.608590955361</v>
+        <v>434.5480142460482</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>10.25</v>
+        <v>183</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>52.13779427754898</v>
+        <v>36.794794519849</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>11.96879764704019</v>
+        <v>16.48753147662475</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.2930866993001373</v>
+        <v>0.6250545271721283</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.08709996149523069</v>
+        <v>-0.8966188293752548</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8105</v>
+        <v>8488</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>428.6634087928583</v>
+        <v>431.608590955361</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>16.05</v>
+        <v>10.25</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>31.18959459236345</v>
+        <v>52.13779427754898</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>30.04267107656997</v>
+        <v>11.96879764704019</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.3569474641568532</v>
+        <v>0.2930866993001373</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.778440624760055</v>
+        <v>0.08709996149523069</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8443</v>
+        <v>8105</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>428.3826625847399</v>
+        <v>428.6634087928583</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>11.4</v>
+        <v>16.05</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>47.76641216413745</v>
+        <v>31.18959459236345</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>47.94406400585044</v>
+        <v>30.04267107656997</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.0859678688462267</v>
+        <v>0.3569474641568532</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.0068744718682293</v>
+        <v>-0.778440624760055</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8093</v>
+        <v>8443</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>425.687139088977</v>
+        <v>428.3826625847399</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>20.25</v>
+        <v>11.4</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>54.03628635106248</v>
+        <v>47.76641216413745</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>10.01049095626087</v>
+        <v>47.94406400585044</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.847939540564822</v>
+        <v>0.0859678688462267</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.0494384880262068</v>
+        <v>-0.0068744718682293</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8932</v>
+        <v>8093</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>419.9999206235317</v>
+        <v>425.687139088977</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>116.5</v>
+        <v>20.25</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>54.85651615066576</v>
+        <v>54.03628635106248</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>28.9649518464179</v>
+        <v>10.01049095626087</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.9738882664716492</v>
+        <v>0.847939540564822</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.4255538249735213</v>
+        <v>-0.0494384880262068</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8404</v>
+        <v>8932</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>419.6364530386554</v>
+        <v>419.9999206235317</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>16.9</v>
+        <v>116.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>51.52500370232336</v>
+        <v>54.85651615066576</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>21.15934974670169</v>
+        <v>28.9649518464179</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.7472917366166879</v>
+        <v>0.9738882664716492</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0402953778986436</v>
+        <v>0.4255538249735213</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>9907</v>
+        <v>8404</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>統一實</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>417.7462898329565</v>
+        <v>419.6364530386554</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>15.1</v>
+        <v>16.9</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>38.69628937730637</v>
+        <v>51.52500370232336</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>25.79256769117899</v>
+        <v>21.15934974670169</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.9126202296479836</v>
+        <v>0.7472917366166879</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0277267338165843</v>
+        <v>0.0402953778986436</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8481</v>
+        <v>9907</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>統一實</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>417.3959186445208</v>
+        <v>417.7462898329565</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>39.9</v>
+        <v>15.1</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>35.29199591567179</v>
+        <v>38.69628937730637</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>18.00055341762568</v>
+        <v>25.79256769117899</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>2.187549494704815</v>
+        <v>0.9126202296479836</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.1399420733690634</v>
+        <v>0.0277267338165843</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>9103</v>
+        <v>8481</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>415.3887674655189</v>
+        <v>417.3959186445208</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>5.18</v>
+        <v>39.9</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>49.80964395169408</v>
+        <v>35.29199591567179</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>14.03008203023474</v>
+        <v>18.00055341762568</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>3.111695686154587</v>
+        <v>2.187549494704815</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.009316664631193799</v>
+        <v>-0.1399420733690634</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8466</v>
+        <v>9103</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>403.0668766798765</v>
+        <v>415.3887674655189</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>17</v>
+        <v>5.18</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>52.88296726561042</v>
+        <v>49.80964395169408</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>26.53599781038028</v>
+        <v>14.03008203023474</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.228763885152016</v>
+        <v>3.111695686154587</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.0268458418497593</v>
+        <v>0.009316664631193799</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8240</v>
+        <v>8466</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>399.1541443836308</v>
+        <v>403.0668766798765</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>42.3</v>
+        <v>17</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>25.70375454447681</v>
+        <v>52.88296726561042</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>26.67400123550372</v>
+        <v>26.53599781038028</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.6752034373823755</v>
+        <v>1.228763885152016</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.5696459004421071</v>
+        <v>-0.0268458418497593</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8390</v>
+        <v>8240</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>396.9511371523531</v>
+        <v>399.1541443836308</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>92.7</v>
+        <v>42.3</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>30.43002910719396</v>
+        <v>25.70375454447681</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>25.58474094037516</v>
+        <v>26.67400123550372</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.7274837884536933</v>
+        <v>0.6752034373823755</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-1.125129434045745</v>
+        <v>-0.5696459004421071</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8442</v>
+        <v>8390</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>396.9309693960192</v>
+        <v>396.9511371523531</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>44.85</v>
+        <v>92.7</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>57.18983204623247</v>
+        <v>30.43002910719396</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>40.21528188753313</v>
+        <v>25.58474094037516</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.5252460518155708</v>
+        <v>0.7274837884536933</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.339268289812183</v>
+        <v>-1.125129434045745</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8103</v>
+        <v>8442</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>392.6372218157684</v>
+        <v>396.9309693960192</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>76.5</v>
+        <v>44.85</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>28.25712183702805</v>
+        <v>57.18983204623247</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>25.56431101271168</v>
+        <v>40.21528188753313</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.9196373900894168</v>
+        <v>0.5252460518155708</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-2.068449098493354</v>
+        <v>0.339268289812183</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8210</v>
+        <v>8103</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>391.6527723729646</v>
+        <v>392.6372218157684</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>1080</v>
+        <v>76.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>34.10292046191579</v>
+        <v>28.25712183702805</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>24.76514248529373</v>
+        <v>25.56431101271168</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.056263813158627</v>
+        <v>0.9196373900894168</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-14.96222174670356</v>
+        <v>-2.068449098493354</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8926</v>
+        <v>8210</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>391.5444931199427</v>
+        <v>391.6527723729646</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>64</v>
+        <v>1080</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>36.02165341104256</v>
+        <v>34.10292046191579</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>30.45440518229228</v>
+        <v>24.76514248529373</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.5219149710283467</v>
+        <v>1.056263813158627</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-1.980820685541556</v>
+        <v>-14.96222174670356</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3495,21 +3495,21 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8299</v>
+        <v>8926</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>391.5089695110924</v>
+        <v>391.5444931199427</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>1735</v>
+        <v>64</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,49 +3520,49 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>30.06317615337719</v>
+        <v>36.02165341104256</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>18.18861078388955</v>
+        <v>30.45440518229228</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.932473476898944</v>
+        <v>0.5219149710283467</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-54.29047887672566</v>
+        <v>-1.980820685541556</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8111</v>
+        <v>8299</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>387.0840233074269</v>
+        <v>391.5089695110924</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>44.25</v>
+        <v>1735</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,49 +3573,49 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>28.61317760324311</v>
+        <v>30.06317615337719</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>25.96229385432875</v>
+        <v>18.18861078388955</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>3.047241785468709</v>
+        <v>0.932473476898944</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.1620223325223877</v>
+        <v>-54.29047887672566</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8478</v>
+        <v>8111</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>385.2129909884111</v>
+        <v>387.0840233074269</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>151</v>
+        <v>44.25</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>43.86285700565237</v>
+        <v>28.61317760324311</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>15.32499458363431</v>
+        <v>25.96229385432875</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6885914757842072</v>
+        <v>3.047241785468709</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.2555169162460702</v>
+        <v>-0.1620223325223877</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8213</v>
+        <v>8478</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>383.7044859804673</v>
+        <v>385.2129909884111</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>30.9</v>
+        <v>151</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>27.37966965774872</v>
+        <v>43.86285700565237</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>23.87415504800938</v>
+        <v>15.32499458363431</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.506563416810919</v>
+        <v>0.6885914757842072</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.3474032863928936</v>
+        <v>-0.2555169162460702</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8215</v>
+        <v>8213</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>382.3595803803656</v>
+        <v>383.7044859804673</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>24.45</v>
+        <v>30.9</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>34.43342584066329</v>
+        <v>27.37966965774872</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>20.03697505022785</v>
+        <v>23.87415504800938</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.6050558896768479</v>
+        <v>1.506563416810919</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.5188979594588511</v>
+        <v>-0.3474032863928936</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>9910</v>
+        <v>8215</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>380.867973185235</v>
+        <v>382.3595803803656</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>68.2</v>
+        <v>24.45</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>44.02304682233773</v>
+        <v>34.43342584066329</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>16.86098544840586</v>
+        <v>20.03697505022785</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.143655668211836</v>
+        <v>0.6050558896768479</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.060507039841724</v>
+        <v>-0.5188979594588511</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>9905</v>
+        <v>9910</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>371.9604810088805</v>
+        <v>380.867973185235</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>20.6</v>
+        <v>68.2</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>41.46795162260218</v>
+        <v>44.02304682233773</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>24.6504478493708</v>
+        <v>16.86098544840586</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.5468842479073307</v>
+        <v>1.143655668211836</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.0617490947930138</v>
+        <v>0.060507039841724</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8147</v>
+        <v>9905</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>371.4412692109866</v>
+        <v>371.9604810088805</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>128.5</v>
+        <v>20.6</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>32.10143898896499</v>
+        <v>41.46795162260218</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>19.50159949926803</v>
+        <v>24.6504478493708</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.8396317699788701</v>
+        <v>0.5468842479073307</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-1.513826687986452</v>
+        <v>-0.0617490947930138</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8473</v>
+        <v>8147</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>370.551438742452</v>
+        <v>371.4412692109866</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>43.6</v>
+        <v>128.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>39.56678661601394</v>
+        <v>32.10143898896499</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>20.88473370305333</v>
+        <v>19.50159949926803</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.6154875724752006</v>
+        <v>0.8396317699788701</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.6026848848676558</v>
+        <v>-1.513826687986452</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8104</v>
+        <v>8473</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>370.5313889011292</v>
+        <v>370.551438742452</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>33.45</v>
+        <v>43.6</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>33.84494711728198</v>
+        <v>39.56678661601394</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>19.2174582572087</v>
+        <v>20.88473370305333</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.1752724531114093</v>
+        <v>0.6154875724752006</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.710071202879317</v>
+        <v>-0.6026848848676558</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8131</v>
+        <v>8104</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>366.1031628205109</v>
+        <v>370.5313889011292</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>67.2</v>
+        <v>33.45</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>42.53812631923978</v>
+        <v>33.84494711728198</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>14.2167833902899</v>
+        <v>19.2174582572087</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.5919251658459365</v>
+        <v>0.1752724531114093</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.9503626830599488</v>
+        <v>-0.710071202879317</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8070</v>
+        <v>8131</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>364.5296055858848</v>
+        <v>366.1031628205109</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>46.7</v>
+        <v>67.2</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>34.11477759672619</v>
+        <v>42.53812631923978</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>19.6807319439278</v>
+        <v>14.2167833902899</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.4595675981768153</v>
+        <v>0.5919251658459365</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,7 +4121,7 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.9718601634583094</v>
+        <v>-0.9503626830599488</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4131,21 +4131,21 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8162</v>
+        <v>8070</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>357.1616873090703</v>
+        <v>364.5296055858848</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>61</v>
+        <v>46.7</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>35.1432591700255</v>
+        <v>34.11477759672619</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>28.49995854880677</v>
+        <v>19.6807319439278</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.8739397595613534</v>
+        <v>0.4595675981768153</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-2.492693204474112</v>
+        <v>-0.9718601634583094</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8454</v>
+        <v>8162</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>348.5473726580755</v>
+        <v>357.1616873090703</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>253.5</v>
+        <v>61</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>39.1128745100719</v>
+        <v>35.1432591700255</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>21.0925851145632</v>
+        <v>28.49995854880677</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.4595708579249234</v>
+        <v>0.8739397595613534</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-6.13663560599683</v>
+        <v>-2.492693204474112</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4237,21 +4237,21 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8171</v>
+        <v>8454</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>329.6827708892724</v>
+        <v>348.5473726580755</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>20.8</v>
+        <v>253.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>45.47093543346924</v>
+        <v>39.1128745100719</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>16.02879174126203</v>
+        <v>21.0925851145632</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.426555995942424</v>
+        <v>0.4595708579249234</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.0460329632027097</v>
+        <v>-6.13663560599683</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8455</v>
+        <v>8171</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>326.4367736786218</v>
+        <v>329.6827708892724</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>24.8</v>
+        <v>20.8</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>38.01252615331278</v>
+        <v>45.47093543346924</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>20.00997350193153</v>
+        <v>16.02879174126203</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.2690118165304508</v>
+        <v>1.426555995942424</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.1010393676820735</v>
+        <v>0.0460329632027097</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8499</v>
+        <v>8455</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>313.2499384843146</v>
+        <v>326.4367736786218</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>269</v>
+        <v>24.8</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>39.82529025363888</v>
+        <v>38.01252615331278</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>13.00803913955954</v>
+        <v>20.00997350193153</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.8251925838420565</v>
+        <v>0.2690118165304508</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-4.033523828536281</v>
+        <v>-0.1010393676820735</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8048</v>
+        <v>8499</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>308.0845245425451</v>
+        <v>313.2499384843146</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>55.1</v>
+        <v>269</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>31.01381501673919</v>
+        <v>39.82529025363888</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>17.29416403681101</v>
+        <v>13.00803913955954</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.7677368775004803</v>
+        <v>0.8251925838420565</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.6899268082477932</v>
+        <v>-4.033523828536281</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8068</v>
+        <v>8048</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>307.8659465645239</v>
+        <v>308.0845245425451</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>18.65</v>
+        <v>55.1</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>45.79139577858005</v>
+        <v>31.01381501673919</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>14.67766659627077</v>
+        <v>17.29416403681101</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.6718612756214281</v>
+        <v>0.7677368775004803</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.06479370212465869</v>
+        <v>-0.6899268082477932</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8112</v>
+        <v>8068</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>307.5614430210653</v>
+        <v>307.8659465645239</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>80.90000000000001</v>
+        <v>18.65</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>36.50382439332736</v>
+        <v>45.79139577858005</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>13.86342463770381</v>
+        <v>14.67766659627077</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.4765246916139745</v>
+        <v>0.6718612756214281</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-1.103514483333838</v>
+        <v>0.06479370212465869</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8084</v>
+        <v>8112</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>304.9100718020537</v>
+        <v>307.5614430210653</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>45.9</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>44.55007495948547</v>
+        <v>36.50382439332736</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>18.23970962719124</v>
+        <v>13.86342463770381</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.285143900641639</v>
+        <v>0.4765246916139745</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.4825051804052064</v>
+        <v>-1.103514483333838</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8054</v>
+        <v>8084</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>302.8679607375613</v>
+        <v>304.9100718020537</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>88.7</v>
+        <v>45.9</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>33.11140364823417</v>
+        <v>44.55007495948547</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>21.38940382089634</v>
+        <v>18.23970962719124</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.3418680353264094</v>
+        <v>1.285143900641639</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>1</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-2.615352357902281</v>
+        <v>-0.4825051804052064</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8076</v>
+        <v>8054</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>301.8782472567674</v>
+        <v>302.8679607375613</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>23</v>
+        <v>88.7</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>35.6274094855786</v>
+        <v>33.11140364823417</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>14.86153701221526</v>
+        <v>21.38940382089634</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.8250819085629445</v>
+        <v>0.3418680353264094</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.3193765140112602</v>
+        <v>-2.615352357902281</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8110</v>
+        <v>8076</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>296.687932383126</v>
+        <v>301.8782472567674</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>41.15</v>
+        <v>23</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>30.43027407429412</v>
+        <v>35.6274094855786</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>18.0208220572255</v>
+        <v>14.86153701221526</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.4010568826924436</v>
+        <v>0.8250819085629445</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-1.342778156524591</v>
+        <v>-0.3193765140112602</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>9955</v>
+        <v>8110</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>284.6319684910669</v>
+        <v>296.687932383126</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>23.9</v>
+        <v>41.15</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>28.68050111870811</v>
+        <v>30.43027407429412</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>27.72678864925133</v>
+        <v>18.0208220572255</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.9082348740622485</v>
+        <v>0.4010568826924436</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.1956309830826477</v>
+        <v>-1.342778156524591</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>9930</v>
+        <v>9955</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>282.7184209014969</v>
+        <v>284.6319684910669</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>63.4</v>
+        <v>23.9</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>31.26732270092597</v>
+        <v>28.68050111870811</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>49.39235385112368</v>
+        <v>27.72678864925133</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.005015203371471</v>
+        <v>0.9082348740622485</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0597080058363528</v>
+        <v>-0.1956309830826477</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4873,21 +4873,21 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>9904</v>
+        <v>9930</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>270.8919014662148</v>
+        <v>282.7184209014969</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>24.35</v>
+        <v>63.4</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>37.27404920859792</v>
+        <v>31.26732270092597</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>21.06008365170581</v>
+        <v>49.39235385112368</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.8739171897574929</v>
+        <v>1.005015203371471</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0191894324978431</v>
+        <v>-0.0597080058363528</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>9136</v>
+        <v>9904</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>270.5244213656657</v>
+        <v>270.8919014662148</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>11.6</v>
+        <v>24.35</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>36.40408603739359</v>
+        <v>37.27404920859792</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>22.36783253435512</v>
+        <v>21.06008365170581</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.5748244585714913</v>
+        <v>0.8739171897574929</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.4024049927445913</v>
+        <v>0.0191894324978431</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>9906</v>
+        <v>9136</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>欣巴巴</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>262.5202745230274</v>
+        <v>270.5244213656657</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>39.5</v>
+        <v>11.6</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>43.34316858927606</v>
+        <v>36.40408603739359</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>22.25499412917491</v>
+        <v>22.36783253435512</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.5228303365349617</v>
+        <v>0.5748244585714913</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.3365621385625379</v>
+        <v>-0.4024049927445913</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8089</v>
+        <v>9906</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>欣巴巴</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>259.2127133125301</v>
+        <v>262.5202745230274</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>18.35</v>
+        <v>39.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>34.18675576529442</v>
+        <v>43.34316858927606</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>23.78599275700904</v>
+        <v>22.25499412917491</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.8213629712374783</v>
+        <v>0.5228303365349617</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.1985568325541248</v>
+        <v>-0.3365621385625379</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8059</v>
+        <v>8089</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>255.56495457672</v>
+        <v>259.2127133125301</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>15.5</v>
+        <v>18.35</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>36.58240758093697</v>
+        <v>34.18675576529442</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>22.53974317663304</v>
+        <v>23.78599275700904</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.7307042930808083</v>
+        <v>0.8213629712374783</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>1</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0282820326562579</v>
+        <v>-0.1985568325541248</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8277</v>
+        <v>8059</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>251.8677941489803</v>
+        <v>255.56495457672</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>7.9</v>
+        <v>15.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>34.86523198529916</v>
+        <v>36.58240758093697</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>23.82878496272343</v>
+        <v>22.53974317663304</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.7380507563177565</v>
+        <v>0.7307042930808083</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.1804472055182256</v>
+        <v>0.0282820326562579</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8249</v>
+        <v>8277</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>250.184248058025</v>
+        <v>251.8677941489803</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>43.65</v>
+        <v>7.9</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>28.86300397807922</v>
+        <v>34.86523198529916</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>15.29717312444641</v>
+        <v>23.82878496272343</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.7080640616967376</v>
+        <v>0.7380507563177565</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.3165110807344926</v>
+        <v>-0.1804472055182256</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8201</v>
+        <v>8249</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>245.7756666515316</v>
+        <v>250.184248058025</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>12.4</v>
+        <v>43.65</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>41.38763310976477</v>
+        <v>28.86300397807922</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>13.73004326193214</v>
+        <v>15.29717312444641</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5731632948891828</v>
+        <v>0.7080640616967376</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.0675880235671633</v>
+        <v>-0.3165110807344926</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8477</v>
+        <v>8201</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>244.28268969514</v>
+        <v>245.7756666515316</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>15.2</v>
+        <v>12.4</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>37.15242913059014</v>
+        <v>41.38763310976477</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>12.7680764896199</v>
+        <v>13.73004326193214</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.6625162782319926</v>
+        <v>0.5731632948891828</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.1009739330615715</v>
+        <v>-0.0675880235671633</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8087</v>
+        <v>8477</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>241.0065654995698</v>
+        <v>244.28268969514</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>26.9</v>
+        <v>15.2</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>25.46595760514008</v>
+        <v>37.15242913059014</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>16.18086017138939</v>
+        <v>12.7680764896199</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.156425018073055</v>
+        <v>0.6625162782319926</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.5132972520617309</v>
+        <v>-0.1009739330615715</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>9802</v>
+        <v>8087</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>240.6913550792188</v>
+        <v>241.0065654995698</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>74.2</v>
+        <v>26.9</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>47.10174050488181</v>
+        <v>25.46595760514008</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>10.91062775433359</v>
+        <v>16.18086017138939</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.059356319899883</v>
+        <v>0.156425018073055</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.1961566054608634</v>
+        <v>-0.5132972520617309</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8422</v>
+        <v>9802</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>232.9108317933049</v>
+        <v>240.6913550792188</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>25.8</v>
+        <v>74.2</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>38.85316261472667</v>
+        <v>47.10174050488181</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>14.13871027061122</v>
+        <v>10.91062775433359</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.6075310050878462</v>
+        <v>1.059356319899883</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.1963960587337506</v>
+        <v>0.1961566054608634</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8049</v>
+        <v>8422</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>229.9267764203604</v>
+        <v>232.9108317933049</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>35.58755997224677</v>
+        <v>38.85316261472667</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>18.59637131813364</v>
+        <v>14.13871027061122</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.324695904726914</v>
+        <v>0.6075310050878462</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.1781314722737861</v>
+        <v>-0.1963960587337506</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8080</v>
+        <v>8049</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>223.8960621654276</v>
+        <v>229.9267764203604</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>26.8</v>
+        <v>25.7</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>35.9121572255637</v>
+        <v>35.58755997224677</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>38.00115857352466</v>
+        <v>18.59637131813364</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.9203430860261228</v>
+        <v>0.324695904726914</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.0973394851735931</v>
+        <v>-0.1781314722737861</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8940</v>
+        <v>8080</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>216.3128689736374</v>
+        <v>223.8960621654276</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>16</v>
+        <v>26.8</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>36.38263723439968</v>
+        <v>35.9121572255637</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>17.48849525321772</v>
+        <v>38.00115857352466</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.507056933722115</v>
+        <v>0.9203430860261228</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0322670438855249</v>
+        <v>-0.0973394851735931</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8085</v>
+        <v>8940</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>197.7041179947152</v>
+        <v>216.3128689736374</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>11.1</v>
+        <v>16</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>36.81115584141291</v>
+        <v>36.38263723439968</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>22.59991097317074</v>
+        <v>17.48849525321772</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.191878751727309</v>
+        <v>1.507056933722115</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0790472104120981</v>
+        <v>-0.0322670438855249</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8467</v>
+        <v>8085</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>196.3552880798136</v>
+        <v>197.7041179947152</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>102</v>
+        <v>11.1</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>41.26604211808932</v>
+        <v>36.81115584141291</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>13.05592819492755</v>
+        <v>22.59991097317074</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>2.048543243394965</v>
+        <v>1.191878751727309</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.7508451126360054</v>
+        <v>-0.0790472104120981</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8101</v>
+        <v>8467</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>194.3726177002769</v>
+        <v>196.3552880798136</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>13.4</v>
+        <v>102</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>47.39393727759823</v>
+        <v>41.26604211808932</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>11.14719740896459</v>
+        <v>13.05592819492755</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.0425528979158186</v>
+        <v>2.048543243394965</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.032941830326481</v>
+        <v>-0.7508451126360054</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8431</v>
+        <v>8101</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>189.2899849465213</v>
+        <v>194.3726177002769</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>46.3</v>
+        <v>13.4</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>36.02225200507795</v>
+        <v>47.39393727759823</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>17.66064641299849</v>
+        <v>11.14719740896459</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.325253676585173</v>
+        <v>0.0425528979158186</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.4519823104303437</v>
+        <v>0.032941830326481</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8423</v>
+        <v>8431</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>177.4177457419045</v>
+        <v>189.2899849465213</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>17.55</v>
+        <v>46.3</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>44.02654173872418</v>
+        <v>36.02225200507795</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>9.966779050265837</v>
+        <v>17.66064641299849</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.017594379447594</v>
+        <v>1.325253676585173</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.009489144294095401</v>
+        <v>-0.4519823104303437</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8429</v>
+        <v>8423</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>176.3200114523451</v>
+        <v>177.4177457419045</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>6.08</v>
+        <v>17.55</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>36.33121305975095</v>
+        <v>44.02654173872418</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>12.93598942566858</v>
+        <v>9.966779050265837</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.8856939788638886</v>
+        <v>1.017594379447594</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.0168570982406815</v>
+        <v>-0.009489144294095401</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8072</v>
+        <v>8429</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>176.1764806657739</v>
+        <v>176.3200114523451</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>26.75</v>
+        <v>6.08</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>36.86901990437292</v>
+        <v>36.33121305975095</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>17.46023508697142</v>
+        <v>12.93598942566858</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.7202081239793905</v>
+        <v>0.8856939788638886</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.296945740883049</v>
+        <v>-0.0168570982406815</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8097</v>
+        <v>8072</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>174.4657915583758</v>
+        <v>176.1764806657739</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>52.3</v>
+        <v>26.75</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>28.03220428245525</v>
+        <v>36.86901990437292</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>14.85774083928837</v>
+        <v>17.46023508697142</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.9352158843810416</v>
+        <v>0.7202081239793905</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.693608023300517</v>
+        <v>-0.296945740883049</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6092,21 +6092,21 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8440</v>
+        <v>8097</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>172.5731781963395</v>
+        <v>174.4657915583758</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>20.2</v>
+        <v>52.3</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>32.59528265900835</v>
+        <v>28.03220428245525</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>13.0946665740224</v>
+        <v>14.85774083928837</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.264666562534456</v>
+        <v>0.9352158843810416</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0913667907137545</v>
+        <v>-0.693608023300517</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>9110</v>
+        <v>8440</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>171.0164501739962</v>
+        <v>172.5731781963395</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>3.11</v>
+        <v>20.2</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>50.3337572909</v>
+        <v>32.59528265900835</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>8.117771399087831</v>
+        <v>13.0946665740224</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.5083069078908783</v>
+        <v>1.264666562534456</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0069308246299152</v>
+        <v>-0.0913667907137545</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8092</v>
+        <v>9110</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>170.6210508679903</v>
+        <v>171.0164501739962</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>13.6</v>
+        <v>3.11</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>38.70978932843306</v>
+        <v>50.3337572909</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>15.31931610404829</v>
+        <v>8.117771399087831</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.5487023894852511</v>
+        <v>0.5083069078908783</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0621326681725789</v>
+        <v>0.0069308246299152</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8487</v>
+        <v>8092</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>156.8655511834135</v>
+        <v>170.6210508679903</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>75.09999999999999</v>
+        <v>13.6</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>36.05327811354281</v>
+        <v>38.70978932843306</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>15.50556710526754</v>
+        <v>15.31931610404829</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.31406341178759</v>
+        <v>0.5487023894852511</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.2388397380193867</v>
+        <v>0.0621326681725789</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8176</v>
+        <v>8487</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>152.3765253416069</v>
+        <v>156.8655511834135</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>9.880000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>41.35435942243586</v>
+        <v>36.05327811354281</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>17.30522010527877</v>
+        <v>15.50556710526754</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.3250477309106204</v>
+        <v>1.31406341178759</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0513693896559195</v>
+        <v>-0.2388397380193867</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>9902</v>
+        <v>8176</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>150.8380156277368</v>
+        <v>152.3765253416069</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>13.5</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>43.67564198279485</v>
+        <v>41.35435942243586</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>13.72156113514578</v>
+        <v>17.30522010527877</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.711596187312217</v>
+        <v>0.3250477309106204</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0143488061619763</v>
+        <v>-0.0513693896559195</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8472</v>
+        <v>9902</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>139.2346234463888</v>
+        <v>150.8380156277368</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>78.59999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>43.93449157166249</v>
+        <v>43.67564198279485</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>12.25263913518639</v>
+        <v>13.72156113514578</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.160336536759134</v>
+        <v>0.711596187312217</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.5856418818821031</v>
+        <v>-0.0143488061619763</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>9911</v>
+        <v>8472</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>櫻花</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>136.4442926488551</v>
+        <v>139.2346234463888</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>83.2</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>46.73430623279845</v>
+        <v>43.93449157166249</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>11.79150516091568</v>
+        <v>12.25263913518639</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.384657436864264</v>
+        <v>0.160336536759134</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0445499223591432</v>
+        <v>-0.5856418818821031</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>8341</v>
+        <v>9911</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>櫻花</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>117.9303133818338</v>
+        <v>136.4442926488551</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>75.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>43.30417074962944</v>
+        <v>46.73430623279845</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>15.31136669498757</v>
+        <v>11.79150516091568</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.7220196667050502</v>
+        <v>1.384657436864264</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0921787773446127</v>
+        <v>-0.0445499223591432</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6569,21 +6569,21 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>8410</v>
+        <v>8341</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>108.4340665790842</v>
+        <v>117.9303133818338</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>31.4</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>30.11618886536186</v>
+        <v>43.30417074962944</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>16.51060530185221</v>
+        <v>15.31136669498757</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.8182063485462331</v>
+        <v>0.7220196667050502</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0421977468182216</v>
+        <v>-0.0921787773446127</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6622,52 +6622,105 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
+        <v>8410</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>森田</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>108.4340665790842</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>30.11618886536186</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>16.51060530185221</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.8182063485462331</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>-0.0421977468182216</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
         <v>8463</v>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>潤泰材</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D117" s="2" t="n">
+      <c r="C118" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="n">
         <v>62.28934733448898</v>
       </c>
-      <c r="E117" s="2" t="n">
+      <c r="E118" s="2" t="n">
         <v>21.3</v>
       </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H117" s="2" t="n">
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
         <v>43.96683941560782</v>
       </c>
-      <c r="I117" s="2" t="n">
+      <c r="I118" s="2" t="n">
         <v>10.32236366802521</v>
       </c>
-      <c r="J117" s="2" t="n">
+      <c r="J118" s="2" t="n">
         <v>1.040546901701477</v>
       </c>
-      <c r="K117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N117" s="2" t="n">
+      <c r="K118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2" t="n">
         <v>0.0149934062470724</v>
       </c>
-      <c r="O117" s="2" t="inlineStr">
+      <c r="O118" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
